--- a/assets/data/imf/catalog/catalogo_dataset_web_ove_fmi_weo.xlsx
+++ b/assets/data/imf/catalog/catalogo_dataset_web_ove_fmi_weo.xlsx
@@ -17,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="[$-es-ES]#,##0"/>
+    <numFmt numFmtId="165" formatCode="[$-es-ES]#,##0.00"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -69,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -83,6 +86,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -114,6 +123,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -144,6 +156,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -601,7 +616,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="I7" s="7" t="n">
         <v>48</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -614,7 +629,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="L7" s="7" t="n">
         <v>5636468000</v>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -679,7 +694,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="I8" s="7" t="n">
         <v>48</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -692,7 +707,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="L8" s="8" t="n">
         <v>4.78039</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
@@ -757,7 +772,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="I9" s="7" t="n">
         <v>8</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -770,7 +785,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="L9" s="7" t="n">
         <v>2383134393000</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
@@ -835,7 +850,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="I10" s="7" t="n">
         <v>38</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -848,7 +863,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="L10" s="4" t="n">
+      <c r="L10" s="8" t="n">
         <v>14.452181</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
@@ -913,7 +928,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="I11" s="7" t="n">
         <v>9</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -926,7 +941,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="L11" s="4" t="n">
+      <c r="L11" s="7" t="n">
         <v>3346413772000</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
@@ -991,7 +1006,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I12" s="4" t="n">
+      <c r="I12" s="7" t="n">
         <v>8</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1004,7 +1019,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="L12" s="4" t="n">
+      <c r="L12" s="7" t="n">
         <v>-963279379000</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
@@ -1069,7 +1084,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="I13" s="7" t="n">
         <v>38</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1082,7 +1097,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="L13" s="4" t="n">
+      <c r="L13" s="8" t="n">
         <v>-5.841671</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
@@ -1147,7 +1162,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I14" s="4" t="n">
+      <c r="I14" s="7" t="n">
         <v>8</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1160,7 +1175,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="L14" s="4" t="n">
+      <c r="L14" s="7" t="n">
         <v>-834225780000</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
@@ -1225,7 +1240,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I15" s="4" t="n">
+      <c r="I15" s="7" t="n">
         <v>38</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1238,7 +1253,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="L15" s="8" t="n">
         <v>-5.059044</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -1303,7 +1318,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I16" s="4" t="n">
+      <c r="I16" s="7" t="n">
         <v>9</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1316,7 +1331,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="L16" s="4" t="n">
+      <c r="L16" s="7" t="n">
         <v>50911791035000</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
@@ -1381,7 +1396,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I17" s="4" t="n">
+      <c r="I17" s="7" t="n">
         <v>28</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1394,7 +1409,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="L17" s="4" t="n">
+      <c r="L17" s="8" t="n">
         <v>308.747344</v>
       </c>
       <c r="M17" s="4" t="inlineStr">
@@ -1459,7 +1474,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I18" s="4" t="n">
+      <c r="I18" s="7" t="n">
         <v>38</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1472,7 +1487,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="L18" s="4" t="n">
+      <c r="L18" s="8" t="n">
         <v>20.293852</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
@@ -1533,7 +1548,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I19" s="4" t="n">
+      <c r="I19" s="7" t="n">
         <v>48</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1546,7 +1561,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L19" s="4" t="n">
+      <c r="L19" s="7" t="n">
         <v>27102199</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -1607,7 +1622,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I20" s="4" t="n">
+      <c r="I20" s="7" t="n">
         <v>20</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1620,7 +1635,7 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="L20" s="4" t="n">
+      <c r="L20" s="8" t="n">
         <v>35.553745</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
@@ -1685,7 +1700,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I21" s="4" t="n">
+      <c r="I21" s="7" t="n">
         <v>11</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1698,7 +1713,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L21" s="4" t="n">
+      <c r="L21" s="7" t="n">
         <v>184820483420000</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
@@ -1763,7 +1778,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I22" s="4" t="n">
+      <c r="I22" s="7" t="n">
         <v>48</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1776,7 +1791,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L22" s="4" t="n">
+      <c r="L22" s="7" t="n">
         <v>117908128000</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
@@ -1841,7 +1856,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I23" s="4" t="n">
+      <c r="I23" s="7" t="n">
         <v>48</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1854,7 +1869,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L23" s="4" t="n">
+      <c r="L23" s="8" t="n">
         <v>4350.500451</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
@@ -1919,7 +1934,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I24" s="4" t="n">
+      <c r="I24" s="7" t="n">
         <v>16</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1932,7 +1947,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L24" s="4" t="n">
+      <c r="L24" s="8" t="n">
         <v>6819390.752229</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
@@ -1993,7 +2008,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I25" s="4" t="n">
+      <c r="I25" s="7" t="n">
         <v>48</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2006,7 +2021,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L25" s="4" t="n">
+      <c r="L25" s="8" t="n">
         <v>8261.804599999999</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
@@ -2071,7 +2086,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I26" s="4" t="n">
+      <c r="I26" s="7" t="n">
         <v>48</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2084,7 +2099,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L26" s="4" t="n">
+      <c r="L26" s="7" t="n">
         <v>8.658552989844166e+16</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
@@ -2149,7 +2164,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I27" s="4" t="n">
+      <c r="I27" s="7" t="n">
         <v>11</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2162,7 +2177,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L27" s="4" t="n">
+      <c r="L27" s="7" t="n">
         <v>184820483420000</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
@@ -2227,7 +2242,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I28" s="4" t="n">
+      <c r="I28" s="7" t="n">
         <v>48</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2240,7 +2255,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L28" s="4" t="n">
+      <c r="L28" s="8" t="n">
         <v>5.9972</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
@@ -2305,7 +2320,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I29" s="4" t="n">
+      <c r="I29" s="7" t="n">
         <v>38</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2318,7 +2333,7 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="L29" s="4" t="n">
+      <c r="L29" s="8" t="n">
         <v>12.624055</v>
       </c>
       <c r="M29" s="4" t="inlineStr">
@@ -2383,7 +2398,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I30" s="4" t="n">
+      <c r="I30" s="7" t="n">
         <v>38</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2396,7 +2411,7 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="L30" s="4" t="n">
+      <c r="L30" s="8" t="n">
         <v>5.111249</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
@@ -2461,7 +2476,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I31" s="4" t="n">
+      <c r="I31" s="7" t="n">
         <v>48</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2474,7 +2489,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L31" s="4" t="n">
+      <c r="L31" s="8" t="n">
         <v>9111677627913.15</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
@@ -2539,7 +2554,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I32" s="4" t="n">
+      <c r="I32" s="7" t="n">
         <v>44</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2552,7 +2567,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L32" s="4" t="n">
+      <c r="L32" s="8" t="n">
         <v>11748900163963.3</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
@@ -2617,7 +2632,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I33" s="4" t="n">
+      <c r="I33" s="7" t="n">
         <v>43</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2630,7 +2645,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L33" s="4" t="n">
+      <c r="L33" s="8" t="n">
         <v>79.585633</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
@@ -2695,7 +2710,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I34" s="4" t="n">
+      <c r="I34" s="7" t="n">
         <v>48</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2708,7 +2723,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L34" s="4" t="n">
+      <c r="L34" s="8" t="n">
         <v>94.37248</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
@@ -2769,7 +2784,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I35" s="4" t="n">
+      <c r="I35" s="7" t="n">
         <v>10</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2782,7 +2797,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L35" s="4" t="n">
+      <c r="L35" s="8" t="n">
         <v>670.73838</v>
       </c>
       <c r="M35" s="4" t="inlineStr">
@@ -2843,7 +2858,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I36" s="4" t="n">
+      <c r="I36" s="7" t="n">
         <v>48</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -2856,7 +2871,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L36" s="4" t="n">
+      <c r="L36" s="7" t="n">
         <v>275547798000</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
@@ -2917,7 +2932,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I37" s="4" t="n">
+      <c r="I37" s="7" t="n">
         <v>48</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2930,7 +2945,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L37" s="4" t="n">
+      <c r="L37" s="8" t="n">
         <v>10166.990517</v>
       </c>
       <c r="M37" s="4" t="inlineStr">
@@ -2995,7 +3010,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I38" s="4" t="n">
+      <c r="I38" s="7" t="n">
         <v>48</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -3008,7 +3023,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L38" s="4" t="n">
+      <c r="L38" s="8" t="n">
         <v>0.117296</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
@@ -3073,7 +3088,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I39" s="4" t="n">
+      <c r="I39" s="7" t="n">
         <v>43</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3086,7 +3101,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L39" s="4" t="n">
+      <c r="L39" s="8" t="n">
         <v>10.051507</v>
       </c>
       <c r="M39" s="4" t="inlineStr">
@@ -3151,7 +3166,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I40" s="4" t="n">
+      <c r="I40" s="7" t="n">
         <v>43</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -3164,7 +3179,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L40" s="4" t="n">
+      <c r="L40" s="8" t="n">
         <v>6.681715</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
@@ -3229,7 +3244,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I41" s="4" t="n">
+      <c r="I41" s="7" t="n">
         <v>45</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -3242,7 +3257,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L41" s="4" t="n">
+      <c r="L41" s="8" t="n">
         <v>-0.907603</v>
       </c>
       <c r="M41" s="4" t="inlineStr">
@@ -3307,7 +3322,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I42" s="4" t="n">
+      <c r="I42" s="7" t="n">
         <v>45</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -3320,7 +3335,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L42" s="4" t="n">
+      <c r="L42" s="8" t="n">
         <v>-1.160338</v>
       </c>
       <c r="M42" s="4" t="inlineStr">
@@ -3458,7 +3473,7 @@
           <t>Número de indicadores</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="7" t="n">
         <v>36</v>
       </c>
     </row>
@@ -3468,7 +3483,7 @@
           <t>Número de registros</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="7" t="n">
         <v>1253</v>
       </c>
     </row>

--- a/assets/data/imf/catalog/catalogo_dataset_web_ove_fmi_weo.xlsx
+++ b/assets/data/imf/catalog/catalogo_dataset_web_ove_fmi_weo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="catalogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="catalogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -82,26 +82,94 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -116,16 +184,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -134,7 +199,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -149,16 +214,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -616,7 +678,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
+      <c r="I7" s="5" t="n">
         <v>48</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -629,7 +691,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L7" s="7" t="n">
+      <c r="L7" s="5" t="n">
         <v>5636468000</v>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -694,7 +756,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I8" s="7" t="n">
+      <c r="I8" s="5" t="n">
         <v>48</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -707,7 +769,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L8" s="8" t="n">
+      <c r="L8" s="6" t="n">
         <v>4.78039</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
@@ -772,7 +834,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I9" s="7" t="n">
+      <c r="I9" s="5" t="n">
         <v>8</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -785,7 +847,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="L9" s="7" t="n">
+      <c r="L9" s="5" t="n">
         <v>2383134393000</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
@@ -850,7 +912,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="I10" s="5" t="n">
         <v>38</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -863,7 +925,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="L10" s="8" t="n">
+      <c r="L10" s="6" t="n">
         <v>14.452181</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
@@ -928,7 +990,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="5" t="n">
         <v>9</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -941,7 +1003,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="L11" s="7" t="n">
+      <c r="L11" s="5" t="n">
         <v>3346413772000</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
@@ -1006,7 +1068,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="I12" s="5" t="n">
         <v>8</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1019,7 +1081,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="L12" s="7" t="n">
+      <c r="L12" s="5" t="n">
         <v>-963279379000</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
@@ -1084,7 +1146,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n">
+      <c r="I13" s="5" t="n">
         <v>38</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1097,7 +1159,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="L13" s="8" t="n">
+      <c r="L13" s="6" t="n">
         <v>-5.841671</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
@@ -1162,7 +1224,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I14" s="7" t="n">
+      <c r="I14" s="5" t="n">
         <v>8</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1175,7 +1237,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="L14" s="7" t="n">
+      <c r="L14" s="5" t="n">
         <v>-834225780000</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
@@ -1240,7 +1302,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I15" s="7" t="n">
+      <c r="I15" s="5" t="n">
         <v>38</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1253,7 +1315,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="L15" s="8" t="n">
+      <c r="L15" s="6" t="n">
         <v>-5.059044</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -1318,7 +1380,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I16" s="7" t="n">
+      <c r="I16" s="5" t="n">
         <v>9</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1331,7 +1393,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="L16" s="7" t="n">
+      <c r="L16" s="5" t="n">
         <v>50911791035000</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
@@ -1396,7 +1458,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I17" s="7" t="n">
+      <c r="I17" s="5" t="n">
         <v>28</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1409,7 +1471,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="L17" s="8" t="n">
+      <c r="L17" s="6" t="n">
         <v>308.747344</v>
       </c>
       <c r="M17" s="4" t="inlineStr">
@@ -1474,7 +1536,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I18" s="7" t="n">
+      <c r="I18" s="5" t="n">
         <v>38</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1487,7 +1549,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="L18" s="8" t="n">
+      <c r="L18" s="6" t="n">
         <v>20.293852</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
@@ -1548,7 +1610,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I19" s="7" t="n">
+      <c r="I19" s="5" t="n">
         <v>48</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1561,7 +1623,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L19" s="7" t="n">
+      <c r="L19" s="5" t="n">
         <v>27102199</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -1622,7 +1684,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I20" s="7" t="n">
+      <c r="I20" s="5" t="n">
         <v>20</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1635,7 +1697,7 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="L20" s="8" t="n">
+      <c r="L20" s="6" t="n">
         <v>35.553745</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
@@ -1700,7 +1762,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I21" s="7" t="n">
+      <c r="I21" s="5" t="n">
         <v>11</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1713,7 +1775,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L21" s="7" t="n">
+      <c r="L21" s="5" t="n">
         <v>184820483420000</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
@@ -1778,7 +1840,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I22" s="7" t="n">
+      <c r="I22" s="5" t="n">
         <v>48</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1791,7 +1853,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L22" s="7" t="n">
+      <c r="L22" s="5" t="n">
         <v>117908128000</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
@@ -1856,7 +1918,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I23" s="7" t="n">
+      <c r="I23" s="5" t="n">
         <v>48</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1869,7 +1931,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L23" s="8" t="n">
+      <c r="L23" s="6" t="n">
         <v>4350.500451</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
@@ -1934,7 +1996,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I24" s="7" t="n">
+      <c r="I24" s="5" t="n">
         <v>16</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1947,7 +2009,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L24" s="8" t="n">
+      <c r="L24" s="6" t="n">
         <v>6819390.752229</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
@@ -2008,7 +2070,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I25" s="7" t="n">
+      <c r="I25" s="5" t="n">
         <v>48</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2021,7 +2083,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L25" s="8" t="n">
+      <c r="L25" s="6" t="n">
         <v>8261.804599999999</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
@@ -2086,7 +2148,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I26" s="7" t="n">
+      <c r="I26" s="5" t="n">
         <v>48</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2099,7 +2161,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L26" s="7" t="n">
+      <c r="L26" s="5" t="n">
         <v>8.658552989844166e+16</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
@@ -2164,7 +2226,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I27" s="7" t="n">
+      <c r="I27" s="5" t="n">
         <v>11</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2177,7 +2239,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L27" s="7" t="n">
+      <c r="L27" s="5" t="n">
         <v>184820483420000</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
@@ -2242,7 +2304,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I28" s="7" t="n">
+      <c r="I28" s="5" t="n">
         <v>48</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2255,7 +2317,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L28" s="8" t="n">
+      <c r="L28" s="6" t="n">
         <v>5.9972</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
@@ -2320,7 +2382,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I29" s="7" t="n">
+      <c r="I29" s="5" t="n">
         <v>38</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2333,7 +2395,7 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="L29" s="8" t="n">
+      <c r="L29" s="6" t="n">
         <v>12.624055</v>
       </c>
       <c r="M29" s="4" t="inlineStr">
@@ -2398,7 +2460,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I30" s="7" t="n">
+      <c r="I30" s="5" t="n">
         <v>38</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2411,7 +2473,7 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="L30" s="8" t="n">
+      <c r="L30" s="6" t="n">
         <v>5.111249</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
@@ -2476,7 +2538,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I31" s="7" t="n">
+      <c r="I31" s="5" t="n">
         <v>48</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2489,7 +2551,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L31" s="8" t="n">
+      <c r="L31" s="6" t="n">
         <v>9111677627913.15</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
@@ -2554,7 +2616,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I32" s="7" t="n">
+      <c r="I32" s="5" t="n">
         <v>44</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2567,7 +2629,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L32" s="8" t="n">
+      <c r="L32" s="6" t="n">
         <v>11748900163963.3</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
@@ -2632,7 +2694,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I33" s="7" t="n">
+      <c r="I33" s="5" t="n">
         <v>43</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2645,7 +2707,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L33" s="8" t="n">
+      <c r="L33" s="6" t="n">
         <v>79.585633</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
@@ -2710,7 +2772,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I34" s="7" t="n">
+      <c r="I34" s="5" t="n">
         <v>48</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2723,7 +2785,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L34" s="8" t="n">
+      <c r="L34" s="6" t="n">
         <v>94.37248</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
@@ -2784,7 +2846,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I35" s="7" t="n">
+      <c r="I35" s="5" t="n">
         <v>10</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2797,7 +2859,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L35" s="8" t="n">
+      <c r="L35" s="6" t="n">
         <v>670.73838</v>
       </c>
       <c r="M35" s="4" t="inlineStr">
@@ -2858,7 +2920,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I36" s="7" t="n">
+      <c r="I36" s="5" t="n">
         <v>48</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -2871,7 +2933,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L36" s="7" t="n">
+      <c r="L36" s="5" t="n">
         <v>275547798000</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
@@ -2932,7 +2994,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I37" s="7" t="n">
+      <c r="I37" s="5" t="n">
         <v>48</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2945,7 +3007,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L37" s="8" t="n">
+      <c r="L37" s="6" t="n">
         <v>10166.990517</v>
       </c>
       <c r="M37" s="4" t="inlineStr">
@@ -3010,7 +3072,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I38" s="7" t="n">
+      <c r="I38" s="5" t="n">
         <v>48</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -3023,7 +3085,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L38" s="8" t="n">
+      <c r="L38" s="6" t="n">
         <v>0.117296</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
@@ -3088,7 +3150,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I39" s="7" t="n">
+      <c r="I39" s="5" t="n">
         <v>43</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3101,7 +3163,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L39" s="8" t="n">
+      <c r="L39" s="6" t="n">
         <v>10.051507</v>
       </c>
       <c r="M39" s="4" t="inlineStr">
@@ -3166,7 +3228,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I40" s="7" t="n">
+      <c r="I40" s="5" t="n">
         <v>43</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -3179,7 +3241,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L40" s="8" t="n">
+      <c r="L40" s="6" t="n">
         <v>6.681715</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
@@ -3244,7 +3306,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I41" s="7" t="n">
+      <c r="I41" s="5" t="n">
         <v>45</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -3257,7 +3319,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L41" s="8" t="n">
+      <c r="L41" s="6" t="n">
         <v>-0.907603</v>
       </c>
       <c r="M41" s="4" t="inlineStr">
@@ -3322,7 +3384,7 @@
           <t>Annual</t>
         </is>
       </c>
-      <c r="I42" s="7" t="n">
+      <c r="I42" s="5" t="n">
         <v>45</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -3335,7 +3397,7 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L42" s="8" t="n">
+      <c r="L42" s="6" t="n">
         <v>-1.160338</v>
       </c>
       <c r="M42" s="4" t="inlineStr">
@@ -3396,19 +3458,19 @@
     <row r="4" ht="16" customHeight="1"/>
     <row r="5" ht="8" customHeight="1"/>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Campo</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Organización</t>
         </is>
@@ -3420,7 +3482,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
@@ -3432,7 +3494,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Fecha generación</t>
         </is>
@@ -3444,7 +3506,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
@@ -3456,7 +3518,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>País</t>
         </is>
@@ -3468,22 +3530,22 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Número de indicadores</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="5" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Número de registros</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="5" t="n">
         <v>1253</v>
       </c>
     </row>

--- a/assets/data/imf/catalog/catalogo_dataset_web_ove_fmi_weo.xlsx
+++ b/assets/data/imf/catalog/catalogo_dataset_web_ove_fmi_weo.xlsx
@@ -3501,7 +3501,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>

--- a/assets/data/imf/catalog/catalogo_dataset_web_ove_fmi_weo.xlsx
+++ b/assets/data/imf/catalog/catalogo_dataset_web_ove_fmi_weo.xlsx
@@ -3501,7 +3501,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>

--- a/assets/data/imf/catalog/catalogo_dataset_web_ove_fmi_weo.xlsx
+++ b/assets/data/imf/catalog/catalogo_dataset_web_ove_fmi_weo.xlsx
@@ -3501,7 +3501,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>

--- a/assets/data/imf/catalog/catalogo_dataset_web_ove_fmi_weo.xlsx
+++ b/assets/data/imf/catalog/catalogo_dataset_web_ove_fmi_weo.xlsx
@@ -3501,7 +3501,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>

--- a/assets/data/imf/catalog/catalogo_dataset_web_ove_fmi_weo.xlsx
+++ b/assets/data/imf/catalog/catalogo_dataset_web_ove_fmi_weo.xlsx
@@ -3501,7 +3501,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
